--- a/data/master_links.xlsx
+++ b/data/master_links.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Crypto\Private\LQDU\LinkBoard\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Crypto\Private\NSFW\LinkBoard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1CC8F0-64DF-467E-8575-1A9FA94CFB47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED40A13C-7843-4390-B4CB-2B9EFC23B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="2145" windowWidth="20730" windowHeight="11280" tabRatio="394" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15960" tabRatio="314" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main_links" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="bdsmvilla" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main_links!$A$1:$U$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main_links!$A$1:$U$156</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2540" uniqueCount="828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2618" uniqueCount="842">
   <si>
     <t>https://xhamster18.desi/videos/nubile-films-seductive-games-of-passion-3267609</t>
   </si>
@@ -1682,9 +1682,6 @@
     <t>ashley fires</t>
   </si>
   <si>
-    <t>chastity cage normal</t>
-  </si>
-  <si>
     <t>lolipop plug</t>
   </si>
   <si>
@@ -2547,6 +2544,51 @@
   </si>
   <si>
     <t>wax at 12m,doggy flogging at 24m,pegging at 31m,piv at 41m</t>
+  </si>
+  <si>
+    <t>https://tube.perverzija.com/whippedass-daisy-marie-and-aiden-starr-daisys-promotion/</t>
+  </si>
+  <si>
+    <t>daisy marie</t>
+  </si>
+  <si>
+    <t>https://tube.perverzija.com/meninpain-bobbi-starr-and-isis-love-the-reward/</t>
+  </si>
+  <si>
+    <t>https://xhamster44.desi/videos/no-safe-word-xh5QQce?pw=</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>https://www.tubebdsm.com/category/bdsm-extreme</t>
+  </si>
+  <si>
+    <t>https://abbdsm.com/video/141957/hot-submissive-teen-18-babe-gets-ass-destroyed-in-anal-sex-domination-fuck/</t>
+  </si>
+  <si>
+    <t>https://xhamster44.desi/videos/clean-and-clear-xhUNQAP?pw=</t>
+  </si>
+  <si>
+    <t>https://www.tubebdsm.com/category/pretty</t>
+  </si>
+  <si>
+    <t>https://www.tubebdsm.com/category/bdsm</t>
+  </si>
+  <si>
+    <t>https://www.tubebdsm.com/category/strap-on-femdom</t>
+  </si>
+  <si>
+    <t>https://www.tubebdsm.com/category/femdom</t>
+  </si>
+  <si>
+    <t>https://xhamster44.desi/videos/chastity-gloves-and-condoms-how-many-until-he-doesnt-feel-anything-xhTMLsQ?pw=</t>
+  </si>
+  <si>
+    <t>malice jade</t>
+  </si>
+  <si>
+    <t>https://www.fapcat.com/videos/2647059/mistress-makes-slave-be-in-chastity-him-too/?utm_source=pbweb&amp;utm_campaign=pbweb</t>
   </si>
 </sst>
 </file>
@@ -3045,7 +3087,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84BC93B7-B882-48B2-AAF6-D1E0B3702CB8}">
-  <dimension ref="A1:U147"/>
+  <dimension ref="A1:U156"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="16" customWidth="1"/>
@@ -3064,7 +3106,7 @@
   <sheetData>
     <row r="1" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>78</v>
@@ -3142,7 +3184,7 @@
         <v>203</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F2" s="17" t="s">
         <v>77</v>
@@ -3157,7 +3199,7 @@
         <v>339</v>
       </c>
       <c r="J2" s="17" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="K2" s="17" t="s">
         <v>173</v>
@@ -3169,7 +3211,7 @@
         <v>102</v>
       </c>
       <c r="N2" s="17" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="O2" s="17" t="s">
         <v>437</v>
@@ -3187,7 +3229,7 @@
         <v>8</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="U2" s="17" t="str" cm="1">
         <f t="array" ref="U2">_xlfn.REGEXEXTRACT(B2,"(?&lt;=//)[^/]+")</f>
@@ -3200,7 +3242,7 @@
         <v>Done</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C3" s="17">
         <v>57</v>
@@ -3209,7 +3251,7 @@
         <v>493</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F3" s="17" t="s">
         <v>77</v>
@@ -3233,10 +3275,10 @@
         <v>118</v>
       </c>
       <c r="M3" s="17" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="N3" s="17" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="O3" s="17" t="s">
         <v>492</v>
@@ -3254,7 +3296,7 @@
         <v>8</v>
       </c>
       <c r="T3" s="17" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="U3" s="17" t="str" cm="1">
         <f t="array" ref="U3">_xlfn.REGEXEXTRACT(B3,"(?&lt;=//)[^/]+")</f>
@@ -3273,10 +3315,10 @@
         <v>0</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F4" s="17" t="s">
         <v>77</v>
@@ -3297,7 +3339,7 @@
         <v>102</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="M4" s="17" t="s">
         <v>118</v>
@@ -3321,7 +3363,7 @@
         <v>8</v>
       </c>
       <c r="T4" s="17" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="U4" s="17" t="str" cm="1">
         <f t="array" ref="U4">_xlfn.REGEXEXTRACT(B4,"(?&lt;=//)[^/]+")</f>
@@ -3334,16 +3376,16 @@
         <v>Done</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C5" s="17">
         <v>0</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>77</v>
@@ -3355,7 +3397,7 @@
         <v>192</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="J5" s="17" t="s">
         <v>400</v>
@@ -3367,16 +3409,16 @@
         <v>193</v>
       </c>
       <c r="M5" s="17" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="N5" s="17" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="O5" s="17" t="s">
+        <v>742</v>
+      </c>
+      <c r="P5" s="17" t="s">
         <v>743</v>
-      </c>
-      <c r="P5" s="17" t="s">
-        <v>744</v>
       </c>
       <c r="Q5" s="17" t="s">
         <v>188</v>
@@ -3388,7 +3430,7 @@
         <v>8</v>
       </c>
       <c r="T5" s="17" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="U5" s="17" t="str" cm="1">
         <f t="array" ref="U5">_xlfn.REGEXEXTRACT(B5,"(?&lt;=//)[^/]+")</f>
@@ -3407,10 +3449,10 @@
         <v>111</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>77</v>
@@ -3425,10 +3467,10 @@
         <v>134</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="L6" s="17" t="s">
         <v>523</v>
@@ -3440,13 +3482,13 @@
         <v>102</v>
       </c>
       <c r="O6" s="17" t="s">
+        <v>655</v>
+      </c>
+      <c r="P6" s="17" t="s">
         <v>656</v>
       </c>
-      <c r="P6" s="17" t="s">
+      <c r="Q6" s="17" t="s">
         <v>657</v>
-      </c>
-      <c r="Q6" s="17" t="s">
-        <v>658</v>
       </c>
       <c r="R6" s="17" t="s">
         <v>91</v>
@@ -3455,7 +3497,7 @@
         <v>7</v>
       </c>
       <c r="T6" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="U6" s="17" t="str" cm="1">
         <f t="array" ref="U6">_xlfn.REGEXEXTRACT(B6,"(?&lt;=//)[^/]+")</f>
@@ -3489,7 +3531,7 @@
         <v>115</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J7" s="17" t="s">
         <v>134</v>
@@ -3535,7 +3577,7 @@
         <v>Done</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C8" s="17">
         <v>73</v>
@@ -3544,7 +3586,7 @@
         <v>320</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>77</v>
@@ -3556,7 +3598,7 @@
         <v>116</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="J8" s="17" t="s">
         <v>120</v>
@@ -3568,16 +3610,16 @@
         <v>118</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="N8" s="17" t="s">
         <v>389</v>
       </c>
       <c r="O8" s="17" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="Q8" s="17" t="s">
         <v>394</v>
@@ -3589,7 +3631,7 @@
         <v>7</v>
       </c>
       <c r="T8" s="17" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="U8" s="17" t="str" cm="1">
         <f t="array" ref="U8">_xlfn.REGEXEXTRACT(B8,"(?&lt;=//)[^/]+")</f>
@@ -3611,7 +3653,7 @@
         <v>131</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>77</v>
@@ -3629,7 +3671,7 @@
         <v>134</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L9" s="17" t="s">
         <v>491</v>
@@ -3644,7 +3686,7 @@
         <v>166</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="Q9" s="17" t="s">
         <v>188</v>
@@ -3656,7 +3698,7 @@
         <v>7</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="U9" s="17" t="str" cm="1">
         <f t="array" ref="U9">_xlfn.REGEXEXTRACT(B9,"(?&lt;=//)[^/]+")</f>
@@ -3937,7 +3979,7 @@
         <v>Done</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C14" s="17">
         <v>46</v>
@@ -3946,7 +3988,7 @@
         <v>190</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F14" s="17" t="s">
         <v>77</v>
@@ -3958,7 +4000,7 @@
         <v>192</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="J14" s="17" t="s">
         <v>153</v>
@@ -3982,7 +4024,7 @@
         <v>188</v>
       </c>
       <c r="Q14" s="17" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="R14" s="17" t="s">
         <v>91</v>
@@ -3991,7 +4033,7 @@
         <v>7</v>
       </c>
       <c r="T14" s="17" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="U14" s="17" t="str" cm="1">
         <f t="array" ref="U14">_xlfn.REGEXEXTRACT(B14,"(?&lt;=//)[^/]+")</f>
@@ -4004,7 +4046,7 @@
         <v>Done</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C15" s="17">
         <v>0</v>
@@ -4013,7 +4055,7 @@
         <v>190</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>77</v>
@@ -4037,7 +4079,7 @@
         <v>339</v>
       </c>
       <c r="M15" s="17" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="N15" s="17" t="s">
         <v>400</v>
@@ -4058,7 +4100,7 @@
         <v>7</v>
       </c>
       <c r="T15" s="17" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="U15" s="17" t="str" cm="1">
         <f t="array" ref="U15">_xlfn.REGEXEXTRACT(B15,"(?&lt;=//)[^/]+")</f>
@@ -4077,7 +4119,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>290</v>
@@ -4138,7 +4180,7 @@
         <v>Done</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C17" s="17">
         <v>0</v>
@@ -4147,7 +4189,7 @@
         <v>190</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F17" s="17" t="s">
         <v>77</v>
@@ -4168,10 +4210,10 @@
         <v>339</v>
       </c>
       <c r="L17" s="17" t="s">
+        <v>704</v>
+      </c>
+      <c r="M17" s="17" t="s">
         <v>705</v>
-      </c>
-      <c r="M17" s="17" t="s">
-        <v>706</v>
       </c>
       <c r="N17" s="17" t="s">
         <v>523</v>
@@ -4192,7 +4234,7 @@
         <v>7</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="U17" s="17" t="str" cm="1">
         <f t="array" ref="U17">_xlfn.REGEXEXTRACT(B17,"(?&lt;=//)[^/]+")</f>
@@ -4205,16 +4247,16 @@
         <v>Done</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C18" s="17">
         <v>0</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>77</v>
@@ -4226,7 +4268,7 @@
         <v>192</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="J18" s="17" t="s">
         <v>400</v>
@@ -4238,7 +4280,7 @@
         <v>195</v>
       </c>
       <c r="M18" s="17" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="N18" s="17" t="s">
         <v>271</v>
@@ -4247,7 +4289,7 @@
         <v>127</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="Q18" s="17" t="s">
         <v>127</v>
@@ -4259,7 +4301,7 @@
         <v>7</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="U18" s="17" t="str" cm="1">
         <f t="array" ref="U18">_xlfn.REGEXEXTRACT(B18,"(?&lt;=//)[^/]+")</f>
@@ -4272,16 +4314,16 @@
         <v>Done</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C19" s="17">
         <v>0</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F19" s="17" t="s">
         <v>77</v>
@@ -4290,7 +4332,7 @@
         <v>77</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="I19" s="17" t="s">
         <v>77</v>
@@ -4311,13 +4353,13 @@
         <v>77</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="P19" s="17" t="s">
         <v>415</v>
       </c>
       <c r="Q19" s="17" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="R19" s="17" t="s">
         <v>91</v>
@@ -4326,7 +4368,7 @@
         <v>7</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="U19" s="17" t="str" cm="1">
         <f t="array" ref="U19">_xlfn.REGEXEXTRACT(B19,"(?&lt;=//)[^/]+")</f>
@@ -4339,16 +4381,16 @@
         <v>Done</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C20" s="17">
         <v>0</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F20" s="17" t="s">
         <v>77</v>
@@ -4357,7 +4399,7 @@
         <v>77</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="I20" s="17" t="s">
         <v>77</v>
@@ -4378,10 +4420,10 @@
         <v>77</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="P20" s="17" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="Q20" s="17" t="s">
         <v>127</v>
@@ -4393,7 +4435,7 @@
         <v>7</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="U20" s="17" t="str" cm="1">
         <f t="array" ref="U20">_xlfn.REGEXEXTRACT(B20,"(?&lt;=//)[^/]+")</f>
@@ -4406,7 +4448,7 @@
         <v>Done</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C21" s="17">
         <v>46</v>
@@ -4415,10 +4457,10 @@
         <v>148</v>
       </c>
       <c r="E21" s="17" t="s">
+        <v>822</v>
+      </c>
+      <c r="F21" s="17" t="s">
         <v>823</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>824</v>
       </c>
       <c r="G21" s="17" t="s">
         <v>77</v>
@@ -4433,16 +4475,16 @@
         <v>134</v>
       </c>
       <c r="K21" s="17" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="L21" s="17" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="M21" s="17" t="s">
         <v>129</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="O21" s="17" t="s">
         <v>486</v>
@@ -4460,7 +4502,7 @@
         <v>7</v>
       </c>
       <c r="T21" s="17" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="U21" s="17" t="str" cm="1">
         <f t="array" ref="U21">_xlfn.REGEXEXTRACT(B21,"(?&lt;=//)[^/]+")</f>
@@ -4473,16 +4515,16 @@
         <v>Done</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C22" s="17">
         <v>113</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>77</v>
@@ -4494,10 +4536,10 @@
         <v>192</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="J22" s="17" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="K22" s="17" t="s">
         <v>397</v>
@@ -4518,16 +4560,16 @@
         <v>127</v>
       </c>
       <c r="Q22" s="17" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="R22" s="17" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="S22" s="17">
         <v>6</v>
       </c>
       <c r="T22" s="17" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="U22" s="17" t="str" cm="1">
         <f t="array" ref="U22">_xlfn.REGEXEXTRACT(B22,"(?&lt;=//)[^/]+")</f>
@@ -4616,7 +4658,7 @@
         <v>148</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F24" s="17" t="s">
         <v>77</v>
@@ -4661,7 +4703,7 @@
         <v>6</v>
       </c>
       <c r="T24" s="17" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="U24" s="17" t="str" cm="1">
         <f t="array" ref="U24">_xlfn.REGEXEXTRACT(B24,"(?&lt;=//)[^/]+")</f>
@@ -4683,7 +4725,7 @@
         <v>525</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F25" s="17" t="s">
         <v>77</v>
@@ -4728,7 +4770,7 @@
         <v>6</v>
       </c>
       <c r="T25" s="17" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="U25" s="17" t="str" cm="1">
         <f t="array" ref="U25">_xlfn.REGEXEXTRACT(B25,"(?&lt;=//)[^/]+")</f>
@@ -4750,7 +4792,7 @@
         <v>131</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>77</v>
@@ -4771,22 +4813,22 @@
         <v>499</v>
       </c>
       <c r="L26" s="17" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="M26" s="17" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="O26" s="17" t="s">
         <v>128</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="Q26" s="17" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="R26" s="17" t="s">
         <v>91</v>
@@ -4795,7 +4837,7 @@
         <v>6</v>
       </c>
       <c r="T26" s="17" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="U26" s="17" t="str" cm="1">
         <f t="array" ref="U26">_xlfn.REGEXEXTRACT(B26,"(?&lt;=//)[^/]+")</f>
@@ -4896,7 +4938,7 @@
         <v>115</v>
       </c>
       <c r="I28" s="17" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J28" s="17" t="s">
         <v>359</v>
@@ -5130,7 +5172,7 @@
         <v>6</v>
       </c>
       <c r="T31" s="17" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="U31" s="17" t="str" cm="1">
         <f t="array" ref="U31">_xlfn.REGEXEXTRACT(B31,"(?&lt;=//)[^/]+")</f>
@@ -5176,7 +5218,7 @@
         <v>353</v>
       </c>
       <c r="M32" s="17" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="N32" s="17" t="s">
         <v>492</v>
@@ -5298,7 +5340,7 @@
         <v>368</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J34" s="17" t="s">
         <v>120</v>
@@ -5411,16 +5453,16 @@
         <v>Done</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C36" s="17">
         <v>20</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F36" s="17" t="s">
         <v>77</v>
@@ -5432,13 +5474,13 @@
         <v>116</v>
       </c>
       <c r="I36" s="17" t="s">
+        <v>666</v>
+      </c>
+      <c r="J36" s="17" t="s">
+        <v>632</v>
+      </c>
+      <c r="K36" s="17" t="s">
         <v>667</v>
-      </c>
-      <c r="J36" s="17" t="s">
-        <v>633</v>
-      </c>
-      <c r="K36" s="17" t="s">
-        <v>668</v>
       </c>
       <c r="L36" s="17" t="s">
         <v>77</v>
@@ -5453,19 +5495,19 @@
         <v>437</v>
       </c>
       <c r="P36" s="17" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Q36" s="17" t="s">
         <v>127</v>
       </c>
       <c r="R36" s="17" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="S36" s="17">
         <v>6</v>
       </c>
       <c r="T36" s="17" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="U36" s="17" t="str" cm="1">
         <f t="array" ref="U36">_xlfn.REGEXEXTRACT(B36,"(?&lt;=//)[^/]+")</f>
@@ -5484,7 +5526,7 @@
         <v>0</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E37" s="17" t="s">
         <v>408</v>
@@ -5499,7 +5541,7 @@
         <v>367</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="J37" s="17" t="s">
         <v>120</v>
@@ -5511,10 +5553,10 @@
         <v>266</v>
       </c>
       <c r="M37" s="17" t="s">
+        <v>606</v>
+      </c>
+      <c r="N37" s="17" t="s">
         <v>607</v>
-      </c>
-      <c r="N37" s="17" t="s">
-        <v>608</v>
       </c>
       <c r="O37" s="17" t="s">
         <v>128</v>
@@ -5532,7 +5574,7 @@
         <v>6</v>
       </c>
       <c r="T37" s="17" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="U37" s="17" t="str" cm="1">
         <f t="array" ref="U37">_xlfn.REGEXEXTRACT(B37,"(?&lt;=//)[^/]+")</f>
@@ -5545,16 +5587,16 @@
         <v>Done</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C38" s="17">
         <v>0</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F38" s="17" t="s">
         <v>77</v>
@@ -5575,7 +5617,7 @@
         <v>107</v>
       </c>
       <c r="L38" s="17" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="M38" s="17" t="s">
         <v>173</v>
@@ -5599,7 +5641,7 @@
         <v>6</v>
       </c>
       <c r="T38" s="17" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="U38" s="17" t="str" cm="1">
         <f t="array" ref="U38">_xlfn.REGEXEXTRACT(B38,"(?&lt;=//)[^/]+")</f>
@@ -5612,7 +5654,7 @@
         <v>Done</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C39" s="17">
         <v>0</v>
@@ -5621,7 +5663,7 @@
         <v>493</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F39" s="17" t="s">
         <v>77</v>
@@ -5666,7 +5708,7 @@
         <v>6</v>
       </c>
       <c r="T39" s="17" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="U39" s="17" t="str" cm="1">
         <f t="array" ref="U39">_xlfn.REGEXEXTRACT(B39,"(?&lt;=//)[^/]+")</f>
@@ -5679,16 +5721,16 @@
         <v>Done</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C40" s="17">
         <v>0</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F40" s="17" t="s">
         <v>77</v>
@@ -5700,7 +5742,7 @@
         <v>192</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="J40" s="17" t="s">
         <v>95</v>
@@ -5709,13 +5751,13 @@
         <v>120</v>
       </c>
       <c r="L40" s="17" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="M40" s="17" t="s">
         <v>519</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="O40" s="17" t="s">
         <v>127</v>
@@ -5733,7 +5775,7 @@
         <v>6</v>
       </c>
       <c r="T40" s="17" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="U40" s="17" t="str" cm="1">
         <f t="array" ref="U40">_xlfn.REGEXEXTRACT(B40,"(?&lt;=//)[^/]+")</f>
@@ -5746,16 +5788,16 @@
         <v>Done</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C41" s="17">
         <v>0</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F41" s="17" t="s">
         <v>77</v>
@@ -5767,19 +5809,19 @@
         <v>192</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="J41" s="17" t="s">
         <v>273</v>
       </c>
       <c r="K41" s="17" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="L41" s="17" t="s">
         <v>469</v>
       </c>
       <c r="M41" s="17" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="N41" s="17" t="s">
         <v>95</v>
@@ -5791,7 +5833,7 @@
         <v>127</v>
       </c>
       <c r="Q41" s="17" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="R41" s="17" t="s">
         <v>91</v>
@@ -5800,7 +5842,7 @@
         <v>6</v>
       </c>
       <c r="T41" s="17" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="U41" s="17" t="str" cm="1">
         <f t="array" ref="U41">_xlfn.REGEXEXTRACT(B41,"(?&lt;=//)[^/]+")</f>
@@ -5813,16 +5855,16 @@
         <v>Done</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C42" s="17">
         <v>0</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F42" s="17" t="s">
         <v>77</v>
@@ -5837,19 +5879,19 @@
         <v>95</v>
       </c>
       <c r="J42" s="17" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="K42" s="17" t="s">
+        <v>753</v>
+      </c>
+      <c r="L42" s="17" t="s">
         <v>754</v>
       </c>
-      <c r="L42" s="17" t="s">
+      <c r="M42" s="17" t="s">
         <v>755</v>
       </c>
-      <c r="M42" s="17" t="s">
+      <c r="N42" s="17" t="s">
         <v>756</v>
-      </c>
-      <c r="N42" s="17" t="s">
-        <v>757</v>
       </c>
       <c r="O42" s="17" t="s">
         <v>127</v>
@@ -5858,7 +5900,7 @@
         <v>362</v>
       </c>
       <c r="Q42" s="17" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="R42" s="17" t="s">
         <v>91</v>
@@ -5867,7 +5909,7 @@
         <v>6</v>
       </c>
       <c r="T42" s="17" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="U42" s="17" t="str" cm="1">
         <f t="array" ref="U42">_xlfn.REGEXEXTRACT(B42,"(?&lt;=//)[^/]+")</f>
@@ -5880,16 +5922,16 @@
         <v>Done</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C43" s="17">
         <v>0</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F43" s="17" t="s">
         <v>77</v>
@@ -5901,19 +5943,19 @@
         <v>192</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="J43" s="17" t="s">
+        <v>758</v>
+      </c>
+      <c r="K43" s="17" t="s">
         <v>759</v>
       </c>
-      <c r="K43" s="17" t="s">
+      <c r="L43" s="17" t="s">
         <v>760</v>
       </c>
-      <c r="L43" s="17" t="s">
+      <c r="M43" s="17" t="s">
         <v>761</v>
-      </c>
-      <c r="M43" s="17" t="s">
-        <v>762</v>
       </c>
       <c r="N43" s="17" t="s">
         <v>400</v>
@@ -5934,7 +5976,7 @@
         <v>6</v>
       </c>
       <c r="T43" s="17" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="U43" s="17" t="str" cm="1">
         <f t="array" ref="U43">_xlfn.REGEXEXTRACT(B43,"(?&lt;=//)[^/]+")</f>
@@ -5947,16 +5989,16 @@
         <v>Done</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C44" s="17">
         <v>0</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E44" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F44" s="17" t="s">
         <v>77</v>
@@ -6001,7 +6043,7 @@
         <v>6</v>
       </c>
       <c r="T44" s="17" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="U44" s="17" t="str" cm="1">
         <f t="array" ref="U44">_xlfn.REGEXEXTRACT(B44,"(?&lt;=//)[^/]+")</f>
@@ -6014,16 +6056,16 @@
         <v>Done</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C45" s="17">
         <v>51</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F45" s="17" t="s">
         <v>77</v>
@@ -6041,7 +6083,7 @@
         <v>134</v>
       </c>
       <c r="K45" s="17" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="L45" s="17" t="s">
         <v>400</v>
@@ -6068,7 +6110,7 @@
         <v>6</v>
       </c>
       <c r="T45" s="17" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="U45" s="17" t="str" cm="1">
         <f t="array" ref="U45">_xlfn.REGEXEXTRACT(B45,"(?&lt;=//)[^/]+")</f>
@@ -6087,13 +6129,13 @@
         <v>129</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G46" s="17" t="s">
         <v>77</v>
@@ -6102,16 +6144,16 @@
         <v>116</v>
       </c>
       <c r="I46" s="17" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J46" s="17" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="K46" s="17" t="s">
         <v>173</v>
       </c>
       <c r="L46" s="17" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="M46" s="17" t="s">
         <v>327</v>
@@ -6129,13 +6171,13 @@
         <v>127</v>
       </c>
       <c r="R46" s="17" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="S46" s="17">
         <v>5</v>
       </c>
       <c r="T46" s="17" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="U46" s="17" t="str" cm="1">
         <f t="array" ref="U46">_xlfn.REGEXEXTRACT(B46,"(?&lt;=//)[^/]+")</f>
@@ -6148,19 +6190,19 @@
         <v>Done</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C47" s="17">
         <v>128</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F47" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G47" s="17" t="s">
         <v>77</v>
@@ -6181,10 +6223,10 @@
         <v>161</v>
       </c>
       <c r="M47" s="17" t="s">
+        <v>687</v>
+      </c>
+      <c r="N47" s="17" t="s">
         <v>688</v>
-      </c>
-      <c r="N47" s="17" t="s">
-        <v>689</v>
       </c>
       <c r="O47" s="17">
         <v>69</v>
@@ -6202,7 +6244,7 @@
         <v>5</v>
       </c>
       <c r="T47" s="17" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="U47" s="17" t="str" cm="1">
         <f t="array" ref="U47">_xlfn.REGEXEXTRACT(B47,"(?&lt;=//)[^/]+")</f>
@@ -6221,10 +6263,10 @@
         <v>116</v>
       </c>
       <c r="D48" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="E48" s="17" t="s">
         <v>661</v>
-      </c>
-      <c r="E48" s="17" t="s">
-        <v>662</v>
       </c>
       <c r="F48" s="17" t="s">
         <v>77</v>
@@ -6242,10 +6284,10 @@
         <v>149</v>
       </c>
       <c r="K48" s="17" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="L48" s="17" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="M48" s="17" t="s">
         <v>102</v>
@@ -6254,13 +6296,13 @@
         <v>118</v>
       </c>
       <c r="O48" s="17" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="P48" s="17" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="Q48" s="17" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="R48" s="17" t="s">
         <v>91</v>
@@ -6269,7 +6311,7 @@
         <v>5</v>
       </c>
       <c r="T48" s="17" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="U48" s="17" t="str" cm="1">
         <f t="array" ref="U48">_xlfn.REGEXEXTRACT(B48,"(?&lt;=//)[^/]+")</f>
@@ -6291,7 +6333,7 @@
         <v>131</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="F49" s="17" t="s">
         <v>217</v>
@@ -6306,7 +6348,7 @@
         <v>134</v>
       </c>
       <c r="J49" s="17" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="K49" s="17" t="s">
         <v>107</v>
@@ -6315,19 +6357,19 @@
         <v>173</v>
       </c>
       <c r="M49" s="17" t="s">
+        <v>649</v>
+      </c>
+      <c r="N49" s="17" t="s">
         <v>650</v>
       </c>
-      <c r="N49" s="17" t="s">
+      <c r="O49" s="17" t="s">
         <v>651</v>
       </c>
-      <c r="O49" s="17" t="s">
+      <c r="P49" s="17" t="s">
+        <v>582</v>
+      </c>
+      <c r="Q49" s="17" t="s">
         <v>652</v>
-      </c>
-      <c r="P49" s="17" t="s">
-        <v>583</v>
-      </c>
-      <c r="Q49" s="17" t="s">
-        <v>653</v>
       </c>
       <c r="R49" s="17" t="s">
         <v>91</v>
@@ -6336,7 +6378,7 @@
         <v>5</v>
       </c>
       <c r="T49" s="17" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="U49" s="17" t="str" cm="1">
         <f t="array" ref="U49">_xlfn.REGEXEXTRACT(B49,"(?&lt;=//)[^/]+")</f>
@@ -6358,7 +6400,7 @@
         <v>148</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F50" s="17" t="s">
         <v>77</v>
@@ -6394,7 +6436,7 @@
         <v>137</v>
       </c>
       <c r="Q50" s="17" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="R50" s="17" t="s">
         <v>91</v>
@@ -6403,7 +6445,7 @@
         <v>5</v>
       </c>
       <c r="T50" s="17" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="U50" s="17" t="str" cm="1">
         <f t="array" ref="U50">_xlfn.REGEXEXTRACT(B50,"(?&lt;=//)[^/]+")</f>
@@ -6425,7 +6467,7 @@
         <v>148</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F51" s="17" t="s">
         <v>77</v>
@@ -6449,7 +6491,7 @@
         <v>107</v>
       </c>
       <c r="M51" s="17" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="N51" s="17" t="s">
         <v>153</v>
@@ -6470,7 +6512,7 @@
         <v>5</v>
       </c>
       <c r="T51" s="17" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="U51" s="17" t="str" cm="1">
         <f t="array" ref="U51">_xlfn.REGEXEXTRACT(B51,"(?&lt;=//)[^/]+")</f>
@@ -6492,7 +6534,7 @@
         <v>525</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="F52" s="17" t="s">
         <v>77</v>
@@ -6525,7 +6567,7 @@
         <v>126</v>
       </c>
       <c r="P52" s="17" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="Q52" s="17" t="s">
         <v>492</v>
@@ -6537,7 +6579,7 @@
         <v>5</v>
       </c>
       <c r="T52" s="17" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="U52" s="17" t="str" cm="1">
         <f t="array" ref="U52">_xlfn.REGEXEXTRACT(B52,"(?&lt;=//)[^/]+")</f>
@@ -6711,22 +6753,22 @@
         <v>153</v>
       </c>
       <c r="K55" s="17" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="L55" s="17" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="M55" s="17" t="s">
         <v>161</v>
       </c>
       <c r="N55" s="17" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="O55" s="17" t="s">
         <v>437</v>
       </c>
       <c r="P55" s="17" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q55" s="17" t="s">
         <v>103</v>
@@ -6738,7 +6780,7 @@
         <v>5</v>
       </c>
       <c r="T55" s="17" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="U55" s="17" t="str" cm="1">
         <f t="array" ref="U55">_xlfn.REGEXEXTRACT(B55,"(?&lt;=//)[^/]+")</f>
@@ -6757,10 +6799,10 @@
         <v>55</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F56" s="17" t="s">
         <v>77</v>
@@ -6772,13 +6814,13 @@
         <v>117</v>
       </c>
       <c r="I56" s="17" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="J56" s="17" t="s">
         <v>118</v>
       </c>
       <c r="K56" s="17" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="L56" s="17" t="s">
         <v>152</v>
@@ -6790,13 +6832,13 @@
         <v>482</v>
       </c>
       <c r="O56" s="17" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="P56" s="17" t="s">
         <v>510</v>
       </c>
       <c r="Q56" s="17" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="R56" s="17" t="s">
         <v>91</v>
@@ -6805,7 +6847,7 @@
         <v>5</v>
       </c>
       <c r="T56" s="17" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="U56" s="17" t="str" cm="1">
         <f t="array" ref="U56">_xlfn.REGEXEXTRACT(B56,"(?&lt;=//)[^/]+")</f>
@@ -6857,7 +6899,7 @@
         <v>523</v>
       </c>
       <c r="O57" s="17" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="P57" s="17" t="s">
         <v>492</v>
@@ -7019,7 +7061,7 @@
         <v>Done</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C60" s="17">
         <v>46</v>
@@ -7028,7 +7070,7 @@
         <v>493</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F60" s="17" t="s">
         <v>77</v>
@@ -7040,16 +7082,16 @@
         <v>116</v>
       </c>
       <c r="I60" s="17" t="s">
+        <v>793</v>
+      </c>
+      <c r="J60" s="17" t="s">
         <v>794</v>
-      </c>
-      <c r="J60" s="17" t="s">
-        <v>795</v>
       </c>
       <c r="K60" s="17" t="s">
         <v>120</v>
       </c>
       <c r="L60" s="17" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="M60" s="17" t="s">
         <v>102</v>
@@ -7073,7 +7115,7 @@
         <v>5</v>
       </c>
       <c r="T60" s="17" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="U60" s="17" t="str" cm="1">
         <f t="array" ref="U60">_xlfn.REGEXEXTRACT(B60,"(?&lt;=//)[^/]+")</f>
@@ -7107,7 +7149,7 @@
         <v>116</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J61" s="17" t="s">
         <v>118</v>
@@ -7128,7 +7170,7 @@
         <v>437</v>
       </c>
       <c r="P61" s="17" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="Q61" s="17" t="s">
         <v>148</v>
@@ -7375,7 +7417,7 @@
         <v>116</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J65" s="17" t="s">
         <v>105</v>
@@ -7421,16 +7463,16 @@
         <v>Done</v>
       </c>
       <c r="B66" s="17" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C66" s="17">
         <v>14</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F66" s="17" t="s">
         <v>77</v>
@@ -7445,7 +7487,7 @@
         <v>477</v>
       </c>
       <c r="J66" s="17" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="K66" s="17" t="s">
         <v>95</v>
@@ -7454,7 +7496,7 @@
         <v>519</v>
       </c>
       <c r="M66" s="17" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N66" s="17" t="s">
         <v>273</v>
@@ -7475,7 +7517,7 @@
         <v>5</v>
       </c>
       <c r="T66" s="17" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="U66" s="17" t="str" cm="1">
         <f t="array" ref="U66">_xlfn.REGEXEXTRACT(B66,"(?&lt;=//)[^/]+")</f>
@@ -7488,25 +7530,25 @@
         <v>Done</v>
       </c>
       <c r="B67" s="17" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C67" s="17">
         <v>11</v>
       </c>
       <c r="D67" s="17" t="s">
+        <v>779</v>
+      </c>
+      <c r="E67" s="17" t="s">
+        <v>729</v>
+      </c>
+      <c r="F67" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G67" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H67" s="17" t="s">
         <v>780</v>
-      </c>
-      <c r="E67" s="17" t="s">
-        <v>730</v>
-      </c>
-      <c r="F67" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="G67" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="H67" s="17" t="s">
-        <v>781</v>
       </c>
       <c r="I67" s="17" t="s">
         <v>264</v>
@@ -7515,7 +7557,7 @@
         <v>101</v>
       </c>
       <c r="K67" s="17" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="L67" s="17" t="s">
         <v>100</v>
@@ -7542,7 +7584,7 @@
         <v>5</v>
       </c>
       <c r="T67" s="17" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="U67" s="17" t="str" cm="1">
         <f t="array" ref="U67">_xlfn.REGEXEXTRACT(B67,"(?&lt;=//)[^/]+")</f>
@@ -7609,7 +7651,7 @@
         <v>5</v>
       </c>
       <c r="T68" s="17" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="U68" s="17" t="str" cm="1">
         <f t="array" ref="U68">_xlfn.REGEXEXTRACT(B68,"(?&lt;=//)[^/]+")</f>
@@ -7689,16 +7731,16 @@
         <v>Done</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C70" s="17">
         <v>1</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E70" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F70" s="17" t="s">
         <v>77</v>
@@ -7719,7 +7761,7 @@
         <v>152</v>
       </c>
       <c r="L70" s="17" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="M70" s="17" t="s">
         <v>77</v>
@@ -7728,7 +7770,7 @@
         <v>77</v>
       </c>
       <c r="O70" s="17" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="P70" s="17" t="s">
         <v>77</v>
@@ -7737,13 +7779,13 @@
         <v>77</v>
       </c>
       <c r="R70" s="17" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="S70" s="17">
         <v>5</v>
       </c>
       <c r="T70" s="17" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="U70" s="17" t="str" cm="1">
         <f t="array" ref="U70">_xlfn.REGEXEXTRACT(B70,"(?&lt;=//)[^/]+")</f>
@@ -7756,16 +7798,16 @@
         <v>Done</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C71" s="17">
         <v>0</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E71" s="17" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F71" s="17" t="s">
         <v>77</v>
@@ -7786,7 +7828,7 @@
         <v>374</v>
       </c>
       <c r="L71" s="17" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="M71" s="17" t="s">
         <v>264</v>
@@ -7810,7 +7852,7 @@
         <v>5</v>
       </c>
       <c r="T71" s="17" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="U71" s="17" t="str" cm="1">
         <f t="array" ref="U71">_xlfn.REGEXEXTRACT(B71,"(?&lt;=//)[^/]+")</f>
@@ -7823,16 +7865,16 @@
         <v>Done</v>
       </c>
       <c r="B72" s="17" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C72" s="17">
         <v>0</v>
       </c>
       <c r="D72" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E72" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F72" s="17" t="s">
         <v>77</v>
@@ -7847,19 +7889,19 @@
         <v>207</v>
       </c>
       <c r="J72" s="17" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="K72" s="17" t="s">
+        <v>748</v>
+      </c>
+      <c r="L72" s="17" t="s">
         <v>749</v>
       </c>
-      <c r="L72" s="17" t="s">
+      <c r="M72" s="17" t="s">
         <v>750</v>
       </c>
-      <c r="M72" s="17" t="s">
+      <c r="N72" s="17" t="s">
         <v>751</v>
-      </c>
-      <c r="N72" s="17" t="s">
-        <v>752</v>
       </c>
       <c r="O72" s="17" t="s">
         <v>127</v>
@@ -7868,7 +7910,7 @@
         <v>103</v>
       </c>
       <c r="Q72" s="17" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="R72" s="17" t="s">
         <v>91</v>
@@ -7877,7 +7919,7 @@
         <v>5</v>
       </c>
       <c r="T72" s="17" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="U72" s="17" t="str" cm="1">
         <f t="array" ref="U72">_xlfn.REGEXEXTRACT(B72,"(?&lt;=//)[^/]+")</f>
@@ -7890,16 +7932,16 @@
         <v>Done</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C73" s="17">
         <v>47</v>
       </c>
       <c r="D73" s="17" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E73" s="17" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="F73" s="17" t="s">
         <v>77</v>
@@ -7929,13 +7971,13 @@
         <v>77</v>
       </c>
       <c r="O73" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="P73" s="17" t="s">
         <v>127</v>
       </c>
       <c r="Q73" s="17" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="R73" s="17" t="s">
         <v>91</v>
@@ -7944,7 +7986,7 @@
         <v>5</v>
       </c>
       <c r="T73" s="17" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="U73" s="17" t="str" cm="1">
         <f t="array" ref="U73">_xlfn.REGEXEXTRACT(B73,"(?&lt;=//)[^/]+")</f>
@@ -7957,19 +7999,19 @@
         <v>Done</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C74" s="17">
         <v>44</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E74" s="17" t="s">
+        <v>816</v>
+      </c>
+      <c r="F74" s="17" t="s">
         <v>817</v>
-      </c>
-      <c r="F74" s="17" t="s">
-        <v>818</v>
       </c>
       <c r="G74" s="17" t="s">
         <v>77</v>
@@ -7993,10 +8035,10 @@
         <v>95</v>
       </c>
       <c r="N74" s="17" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="O74" s="17" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="P74" s="17" t="s">
         <v>127</v>
@@ -8011,7 +8053,7 @@
         <v>5</v>
       </c>
       <c r="T74" s="17" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="U74" s="17" t="str" cm="1">
         <f t="array" ref="U74">_xlfn.REGEXEXTRACT(B74,"(?&lt;=//)[^/]+")</f>
@@ -8024,7 +8066,7 @@
         <v>Done</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C75" s="17">
         <v>54</v>
@@ -8033,7 +8075,7 @@
         <v>190</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="F75" s="17" t="s">
         <v>77</v>
@@ -8078,7 +8120,7 @@
         <v>5</v>
       </c>
       <c r="T75" s="17" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="U75" s="17" t="str" cm="1">
         <f t="array" ref="U75">_xlfn.REGEXEXTRACT(B75,"(?&lt;=//)[^/]+")</f>
@@ -8097,10 +8139,10 @@
         <v>182</v>
       </c>
       <c r="D76" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E76" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F76" s="17" t="s">
         <v>77</v>
@@ -8112,10 +8154,10 @@
         <v>116</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J76" s="17" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="K76" s="17" t="s">
         <v>100</v>
@@ -8124,19 +8166,19 @@
         <v>485</v>
       </c>
       <c r="M76" s="17" t="s">
+        <v>682</v>
+      </c>
+      <c r="N76" s="17" t="s">
         <v>683</v>
-      </c>
-      <c r="N76" s="17" t="s">
-        <v>684</v>
       </c>
       <c r="O76" s="17" t="s">
         <v>188</v>
       </c>
       <c r="P76" s="17" t="s">
+        <v>684</v>
+      </c>
+      <c r="Q76" s="17" t="s">
         <v>685</v>
-      </c>
-      <c r="Q76" s="17" t="s">
-        <v>686</v>
       </c>
       <c r="R76" s="17" t="s">
         <v>91</v>
@@ -8145,7 +8187,7 @@
         <v>4</v>
       </c>
       <c r="T76" s="17" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="U76" s="17" t="str" cm="1">
         <f t="array" ref="U76">_xlfn.REGEXEXTRACT(B76,"(?&lt;=//)[^/]+")</f>
@@ -8164,13 +8206,13 @@
         <v>170</v>
       </c>
       <c r="D77" s="17" t="s">
+        <v>672</v>
+      </c>
+      <c r="E77" s="17" t="s">
         <v>673</v>
       </c>
-      <c r="E77" s="17" t="s">
+      <c r="F77" s="17" t="s">
         <v>674</v>
-      </c>
-      <c r="F77" s="17" t="s">
-        <v>675</v>
       </c>
       <c r="G77" s="17" t="s">
         <v>77</v>
@@ -8188,19 +8230,19 @@
         <v>153</v>
       </c>
       <c r="L77" s="17" t="s">
+        <v>678</v>
+      </c>
+      <c r="M77" s="17" t="s">
         <v>679</v>
       </c>
-      <c r="M77" s="17" t="s">
+      <c r="N77" s="17" t="s">
         <v>680</v>
-      </c>
-      <c r="N77" s="17" t="s">
-        <v>681</v>
       </c>
       <c r="O77" s="17" t="s">
         <v>188</v>
       </c>
       <c r="P77" s="17" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="Q77" s="17" t="s">
         <v>510</v>
@@ -8212,7 +8254,7 @@
         <v>4</v>
       </c>
       <c r="T77" s="17" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="U77" s="17" t="str" cm="1">
         <f t="array" ref="U77">_xlfn.REGEXEXTRACT(B77,"(?&lt;=//)[^/]+")</f>
@@ -8264,7 +8306,7 @@
         <v>77</v>
       </c>
       <c r="O78" s="17" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="P78" s="17" t="s">
         <v>188</v>
@@ -8365,10 +8407,10 @@
         <v>66</v>
       </c>
       <c r="D80" s="17" t="s">
+        <v>621</v>
+      </c>
+      <c r="E80" s="17" t="s">
         <v>622</v>
-      </c>
-      <c r="E80" s="17" t="s">
-        <v>623</v>
       </c>
       <c r="F80" s="17" t="s">
         <v>77</v>
@@ -8380,7 +8422,7 @@
         <v>367</v>
       </c>
       <c r="I80" s="17" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="J80" s="17" t="s">
         <v>339</v>
@@ -8392,19 +8434,19 @@
         <v>120</v>
       </c>
       <c r="M80" s="17" t="s">
+        <v>627</v>
+      </c>
+      <c r="N80" s="17" t="s">
         <v>628</v>
-      </c>
-      <c r="N80" s="17" t="s">
-        <v>629</v>
       </c>
       <c r="O80" s="17" t="s">
         <v>188</v>
       </c>
       <c r="P80" s="17" t="s">
+        <v>625</v>
+      </c>
+      <c r="Q80" s="17" t="s">
         <v>626</v>
-      </c>
-      <c r="Q80" s="17" t="s">
-        <v>627</v>
       </c>
       <c r="R80" s="17" t="s">
         <v>91</v>
@@ -8413,7 +8455,7 @@
         <v>4</v>
       </c>
       <c r="T80" s="17" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="U80" s="17" t="str" cm="1">
         <f t="array" ref="U80">_xlfn.REGEXEXTRACT(B80,"(?&lt;=//)[^/]+")</f>
@@ -8435,10 +8477,10 @@
         <v>320</v>
       </c>
       <c r="E81" s="17" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F81" s="17" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G81" s="17" t="s">
         <v>77</v>
@@ -8471,7 +8513,7 @@
         <v>127</v>
       </c>
       <c r="Q81" s="17" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="R81" s="17" t="s">
         <v>91</v>
@@ -8480,7 +8522,7 @@
         <v>4</v>
       </c>
       <c r="T81" s="17" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="U81" s="17" t="str" cm="1">
         <f t="array" ref="U81">_xlfn.REGEXEXTRACT(B81,"(?&lt;=//)[^/]+")</f>
@@ -8569,10 +8611,10 @@
         <v>131</v>
       </c>
       <c r="E83" s="17" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F83" s="17" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="G83" s="17" t="s">
         <v>77</v>
@@ -8584,10 +8626,10 @@
         <v>102</v>
       </c>
       <c r="J83" s="17" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="K83" s="17" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="L83" s="17" t="s">
         <v>133</v>
@@ -8605,7 +8647,7 @@
         <v>362</v>
       </c>
       <c r="Q83" s="17" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="R83" s="17" t="s">
         <v>91</v>
@@ -8614,7 +8656,7 @@
         <v>4</v>
       </c>
       <c r="T83" s="17" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U83" s="17" t="str" cm="1">
         <f t="array" ref="U83">_xlfn.REGEXEXTRACT(B83,"(?&lt;=//)[^/]+")</f>
@@ -8715,13 +8757,13 @@
         <v>117</v>
       </c>
       <c r="I85" s="17" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="J85" s="17" t="s">
         <v>398</v>
       </c>
       <c r="K85" s="17" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="L85" s="17" t="s">
         <v>134</v>
@@ -8730,7 +8772,7 @@
         <v>533</v>
       </c>
       <c r="N85" s="17" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="O85" s="17">
         <v>69</v>
@@ -8739,7 +8781,7 @@
         <v>228</v>
       </c>
       <c r="Q85" s="17" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="R85" s="17" t="s">
         <v>91</v>
@@ -8748,7 +8790,7 @@
         <v>4</v>
       </c>
       <c r="T85" s="17" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="U85" s="17" t="str" cm="1">
         <f t="array" ref="U85">_xlfn.REGEXEXTRACT(B85,"(?&lt;=//)[^/]+")</f>
@@ -8770,7 +8812,7 @@
         <v>148</v>
       </c>
       <c r="E86" s="17" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F86" s="17" t="s">
         <v>77</v>
@@ -8800,10 +8842,10 @@
         <v>153</v>
       </c>
       <c r="O86" s="17" t="s">
+        <v>547</v>
+      </c>
+      <c r="P86" s="17" t="s">
         <v>548</v>
-      </c>
-      <c r="P86" s="17" t="s">
-        <v>549</v>
       </c>
       <c r="Q86" s="17" t="s">
         <v>137</v>
@@ -8815,7 +8857,7 @@
         <v>4</v>
       </c>
       <c r="T86" s="17" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="U86" s="17" t="str" cm="1">
         <f t="array" ref="U86">_xlfn.REGEXEXTRACT(B86,"(?&lt;=//)[^/]+")</f>
@@ -8837,7 +8879,7 @@
         <v>348</v>
       </c>
       <c r="E87" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F87" s="17" t="s">
         <v>77</v>
@@ -9102,7 +9144,7 @@
         <v>44</v>
       </c>
       <c r="D91" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E91" s="17" t="s">
         <v>473</v>
@@ -9498,7 +9540,7 @@
         <v>Done</v>
       </c>
       <c r="B97" s="17" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C97" s="17">
         <v>22</v>
@@ -9507,7 +9549,7 @@
         <v>268</v>
       </c>
       <c r="E97" s="17" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="F97" s="17" t="s">
         <v>77</v>
@@ -9519,7 +9561,7 @@
         <v>192</v>
       </c>
       <c r="I97" s="17" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="J97" s="17" t="s">
         <v>118</v>
@@ -9531,13 +9573,13 @@
         <v>134</v>
       </c>
       <c r="M97" s="17" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="N97" s="17" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="O97" s="17" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="P97" s="17" t="s">
         <v>127</v>
@@ -9552,7 +9594,7 @@
         <v>4</v>
       </c>
       <c r="T97" s="17" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="U97" s="17" t="str" cm="1">
         <f t="array" ref="U97">_xlfn.REGEXEXTRACT(B97,"(?&lt;=//)[^/]+")</f>
@@ -9662,7 +9704,7 @@
         <v>161</v>
       </c>
       <c r="L99" s="17" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="M99" s="17" t="s">
         <v>327</v>
@@ -9839,10 +9881,10 @@
         <v>0</v>
       </c>
       <c r="D102" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E102" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F102" s="17" t="s">
         <v>77</v>
@@ -9851,7 +9893,7 @@
         <v>77</v>
       </c>
       <c r="H102" s="17" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="I102" s="17" t="s">
         <v>77</v>
@@ -9887,7 +9929,7 @@
         <v>4</v>
       </c>
       <c r="T102" s="17" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="U102" s="17" t="str" cm="1">
         <f t="array" ref="U102">_xlfn.REGEXEXTRACT(B102,"(?&lt;=//)[^/]+")</f>
@@ -9906,10 +9948,10 @@
         <v>0</v>
       </c>
       <c r="D103" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E103" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F103" s="17" t="s">
         <v>77</v>
@@ -9918,7 +9960,7 @@
         <v>77</v>
       </c>
       <c r="H103" s="17" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="I103" s="17" t="s">
         <v>77</v>
@@ -9954,7 +9996,7 @@
         <v>4</v>
       </c>
       <c r="T103" s="17" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="U103" s="17" t="str" cm="1">
         <f t="array" ref="U103">_xlfn.REGEXEXTRACT(B103,"(?&lt;=//)[^/]+")</f>
@@ -9967,16 +10009,16 @@
         <v>Done</v>
       </c>
       <c r="B104" s="17" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C104" s="17">
         <v>0</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E104" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F104" s="17" t="s">
         <v>77</v>
@@ -9988,13 +10030,13 @@
         <v>192</v>
       </c>
       <c r="I104" s="17" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="J104" s="17" t="s">
+        <v>704</v>
+      </c>
+      <c r="K104" s="17" t="s">
         <v>705</v>
-      </c>
-      <c r="K104" s="17" t="s">
-        <v>706</v>
       </c>
       <c r="L104" s="17" t="s">
         <v>134</v>
@@ -10015,13 +10057,13 @@
         <v>437</v>
       </c>
       <c r="R104" s="17" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="S104" s="17">
         <v>4</v>
       </c>
       <c r="T104" s="17" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="U104" s="17" t="str" cm="1">
         <f t="array" ref="U104">_xlfn.REGEXEXTRACT(B104,"(?&lt;=//)[^/]+")</f>
@@ -10034,16 +10076,16 @@
         <v>Done</v>
       </c>
       <c r="B105" s="17" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C105" s="17">
         <v>44</v>
       </c>
       <c r="D105" s="17" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E105" s="17" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="F105" s="17" t="s">
         <v>77</v>
@@ -10070,7 +10112,7 @@
         <v>118</v>
       </c>
       <c r="N105" s="17" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="O105" s="17" t="s">
         <v>188</v>
@@ -10088,7 +10130,7 @@
         <v>4</v>
       </c>
       <c r="T105" s="17" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="U105" s="17" t="str" cm="1">
         <f t="array" ref="U105">_xlfn.REGEXEXTRACT(B105,"(?&lt;=//)[^/]+")</f>
@@ -10101,19 +10143,19 @@
         <v>Done</v>
       </c>
       <c r="B106" s="17" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C106" s="17">
         <v>42</v>
       </c>
       <c r="D106" s="17" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E106" s="17" t="s">
+        <v>813</v>
+      </c>
+      <c r="F106" s="17" t="s">
         <v>814</v>
-      </c>
-      <c r="F106" s="17" t="s">
-        <v>815</v>
       </c>
       <c r="G106" s="17" t="s">
         <v>77</v>
@@ -10125,7 +10167,7 @@
         <v>134</v>
       </c>
       <c r="J106" s="17" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="K106" s="17" t="s">
         <v>95</v>
@@ -10137,7 +10179,7 @@
         <v>118</v>
       </c>
       <c r="N106" s="17" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="O106" s="17" t="s">
         <v>437</v>
@@ -10155,7 +10197,7 @@
         <v>4</v>
       </c>
       <c r="T106" s="17" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="U106" s="17" t="str" cm="1">
         <f t="array" ref="U106">_xlfn.REGEXEXTRACT(B106,"(?&lt;=//)[^/]+")</f>
@@ -10168,19 +10210,19 @@
         <v>Done</v>
       </c>
       <c r="B107" s="17" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C107" s="17">
         <v>106</v>
       </c>
       <c r="D107" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E107" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F107" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G107" s="17" t="s">
         <v>77</v>
@@ -10189,22 +10231,22 @@
         <v>192</v>
       </c>
       <c r="I107" s="17" t="s">
+        <v>707</v>
+      </c>
+      <c r="J107" s="17" t="s">
         <v>708</v>
       </c>
-      <c r="J107" s="17" t="s">
-        <v>709</v>
-      </c>
       <c r="K107" s="17" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="L107" s="17" t="s">
+        <v>782</v>
+      </c>
+      <c r="M107" s="17" t="s">
         <v>783</v>
       </c>
-      <c r="M107" s="17" t="s">
-        <v>784</v>
-      </c>
       <c r="N107" s="17" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="O107" s="17" t="s">
         <v>188</v>
@@ -10216,13 +10258,13 @@
         <v>437</v>
       </c>
       <c r="R107" s="17" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="S107" s="17">
         <v>3</v>
       </c>
       <c r="T107" s="17" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="U107" s="17" t="str" cm="1">
         <f t="array" ref="U107">_xlfn.REGEXEXTRACT(B107,"(?&lt;=//)[^/]+")</f>
@@ -10329,7 +10371,7 @@
         <v>102</v>
       </c>
       <c r="K109" s="17" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="L109" s="17" t="s">
         <v>134</v>
@@ -10356,7 +10398,7 @@
         <v>3</v>
       </c>
       <c r="T109" s="17" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="U109" s="17" t="str" cm="1">
         <f t="array" ref="U109">_xlfn.REGEXEXTRACT(B109,"(?&lt;=//)[^/]+")</f>
@@ -10378,7 +10420,7 @@
         <v>147</v>
       </c>
       <c r="E110" s="17" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="F110" s="17" t="s">
         <v>77</v>
@@ -10393,16 +10435,16 @@
         <v>133</v>
       </c>
       <c r="J110" s="17" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="K110" s="17" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="L110" s="17" t="s">
         <v>107</v>
       </c>
       <c r="M110" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="N110" s="17" t="s">
         <v>100</v>
@@ -10411,10 +10453,10 @@
         <v>148</v>
       </c>
       <c r="P110" s="17" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="Q110" s="17" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="R110" s="17" t="s">
         <v>91</v>
@@ -10423,7 +10465,7 @@
         <v>3</v>
       </c>
       <c r="T110" s="17" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="U110" s="17" t="str" cm="1">
         <f t="array" ref="U110">_xlfn.REGEXEXTRACT(B110,"(?&lt;=//)[^/]+")</f>
@@ -10527,10 +10569,10 @@
         <v>134</v>
       </c>
       <c r="J112" s="17" t="s">
+        <v>736</v>
+      </c>
+      <c r="K112" s="17" t="s">
         <v>539</v>
-      </c>
-      <c r="K112" s="17" t="s">
-        <v>540</v>
       </c>
       <c r="L112" s="17" t="s">
         <v>95</v>
@@ -10539,7 +10581,7 @@
         <v>523</v>
       </c>
       <c r="N112" s="17" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="O112" s="17" t="s">
         <v>188</v>
@@ -10557,7 +10599,7 @@
         <v>3</v>
       </c>
       <c r="T112" s="17" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="U112" s="17" t="str" cm="1">
         <f t="array" ref="U112">_xlfn.REGEXEXTRACT(B112,"(?&lt;=//)[^/]+")</f>
@@ -10597,7 +10639,7 @@
         <v>211</v>
       </c>
       <c r="K113" s="17" t="s">
-        <v>539</v>
+        <v>736</v>
       </c>
       <c r="L113" s="17" t="s">
         <v>212</v>
@@ -10670,7 +10712,7 @@
         <v>152</v>
       </c>
       <c r="M114" s="17" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="N114" s="17" t="s">
         <v>499</v>
@@ -10704,13 +10746,13 @@
         <v>Done</v>
       </c>
       <c r="B115" s="17" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C115" s="17">
         <v>46</v>
       </c>
       <c r="D115" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E115" s="17" t="s">
         <v>365</v>
@@ -11596,7 +11638,7 @@
         <v>116</v>
       </c>
       <c r="I128" s="17" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J128" s="17" t="s">
         <v>112</v>
@@ -11642,16 +11684,16 @@
         <v>Done</v>
       </c>
       <c r="B129" s="17" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C129" s="17">
         <v>5</v>
       </c>
       <c r="D129" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E129" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F129" s="17" t="s">
         <v>77</v>
@@ -11663,10 +11705,10 @@
         <v>192</v>
       </c>
       <c r="I129" s="17" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="J129" s="17" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="K129" s="17" t="s">
         <v>77</v>
@@ -11690,13 +11732,13 @@
         <v>77</v>
       </c>
       <c r="R129" s="17" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="S129" s="17">
         <v>3</v>
       </c>
       <c r="T129" s="17" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="U129" s="17" t="str" cm="1">
         <f t="array" ref="U129">_xlfn.REGEXEXTRACT(B129,"(?&lt;=//)[^/]+")</f>
@@ -11709,7 +11751,7 @@
         <v>Done</v>
       </c>
       <c r="B130" s="17" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C130" s="17">
         <v>4</v>
@@ -11718,7 +11760,7 @@
         <v>190</v>
       </c>
       <c r="E130" s="17" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="F130" s="17" t="s">
         <v>77</v>
@@ -11736,7 +11778,7 @@
         <v>120</v>
       </c>
       <c r="K130" s="17" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="L130" s="17" t="s">
         <v>77</v>
@@ -11763,7 +11805,7 @@
         <v>3</v>
       </c>
       <c r="T130" s="17" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="U130" s="17" t="str" cm="1">
         <f t="array" ref="U130">_xlfn.REGEXEXTRACT(B130,"(?&lt;=//)[^/]+")</f>
@@ -11782,7 +11824,7 @@
         <v>0</v>
       </c>
       <c r="D131" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E131" s="17" t="s">
         <v>347</v>
@@ -11797,7 +11839,7 @@
         <v>116</v>
       </c>
       <c r="I131" s="17" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J131" s="17" t="s">
         <v>134</v>
@@ -11830,7 +11872,7 @@
         <v>3</v>
       </c>
       <c r="T131" s="17" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="U131" s="17" t="str" cm="1">
         <f t="array" ref="U131">_xlfn.REGEXEXTRACT(B131,"(?&lt;=//)[^/]+")</f>
@@ -11849,7 +11891,7 @@
         <v>0</v>
       </c>
       <c r="D132" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E132" s="17" t="s">
         <v>401</v>
@@ -11864,7 +11906,7 @@
         <v>116</v>
       </c>
       <c r="I132" s="17" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J132" s="17" t="s">
         <v>134</v>
@@ -11873,7 +11915,7 @@
         <v>173</v>
       </c>
       <c r="L132" s="17" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="M132" s="17" t="s">
         <v>102</v>
@@ -11885,7 +11927,7 @@
         <v>188</v>
       </c>
       <c r="P132" s="17" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q132" s="17" t="s">
         <v>103</v>
@@ -11897,7 +11939,7 @@
         <v>3</v>
       </c>
       <c r="T132" s="17" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="U132" s="17" t="str" cm="1">
         <f t="array" ref="U132">_xlfn.REGEXEXTRACT(B132,"(?&lt;=//)[^/]+")</f>
@@ -11916,10 +11958,10 @@
         <v>64</v>
       </c>
       <c r="D133" s="17" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E133" s="17" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F133" s="17" t="s">
         <v>77</v>
@@ -11934,10 +11976,10 @@
         <v>339</v>
       </c>
       <c r="J133" s="17" t="s">
+        <v>597</v>
+      </c>
+      <c r="K133" s="17" t="s">
         <v>598</v>
-      </c>
-      <c r="K133" s="17" t="s">
-        <v>599</v>
       </c>
       <c r="L133" s="17" t="s">
         <v>161</v>
@@ -11955,7 +11997,7 @@
         <v>387</v>
       </c>
       <c r="Q133" s="17" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="R133" s="17" t="s">
         <v>91</v>
@@ -11964,7 +12006,7 @@
         <v>2</v>
       </c>
       <c r="T133" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="U133" s="17" t="str" cm="1">
         <f t="array" ref="U133">_xlfn.REGEXEXTRACT(B133,"(?&lt;=//)[^/]+")</f>
@@ -11983,10 +12025,10 @@
         <v>57</v>
       </c>
       <c r="D134" s="17" t="s">
+        <v>578</v>
+      </c>
+      <c r="E134" s="17" t="s">
         <v>579</v>
-      </c>
-      <c r="E134" s="17" t="s">
-        <v>580</v>
       </c>
       <c r="F134" s="17" t="s">
         <v>77</v>
@@ -12022,7 +12064,7 @@
         <v>415</v>
       </c>
       <c r="Q134" s="17" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="R134" s="17" t="s">
         <v>91</v>
@@ -12031,7 +12073,7 @@
         <v>2</v>
       </c>
       <c r="T134" s="17" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="U134" s="17" t="str" cm="1">
         <f t="array" ref="U134">_xlfn.REGEXEXTRACT(B134,"(?&lt;=//)[^/]+")</f>
@@ -12056,7 +12098,7 @@
         <v>454</v>
       </c>
       <c r="F135" s="17" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="G135" s="17" t="s">
         <v>77</v>
@@ -12083,7 +12125,7 @@
         <v>77</v>
       </c>
       <c r="O135" s="17" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P135" s="17" t="s">
         <v>394</v>
@@ -12098,7 +12140,7 @@
         <v>2</v>
       </c>
       <c r="T135" s="17" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="U135" s="17" t="str" cm="1">
         <f t="array" ref="U135">_xlfn.REGEXEXTRACT(B135,"(?&lt;=//)[^/]+")</f>
@@ -12284,7 +12326,7 @@
         <v>77</v>
       </c>
       <c r="O138" s="17" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="P138" s="17" t="s">
         <v>77</v>
@@ -12385,7 +12427,7 @@
         <v>18</v>
       </c>
       <c r="D140" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E140" s="17" t="s">
         <v>276</v>
@@ -12400,7 +12442,7 @@
         <v>115</v>
       </c>
       <c r="I140" s="17" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J140" s="17" t="s">
         <v>278</v>
@@ -12433,7 +12475,7 @@
         <v>2</v>
       </c>
       <c r="T140" s="17" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="U140" s="17" t="str" cm="1">
         <f t="array" ref="U140">_xlfn.REGEXEXTRACT(B140,"(?&lt;=//)[^/]+")</f>
@@ -12500,7 +12542,7 @@
         <v>2</v>
       </c>
       <c r="T141" s="17" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="U141" s="17" t="str" cm="1">
         <f t="array" ref="U141">_xlfn.REGEXEXTRACT(B141,"(?&lt;=//)[^/]+")</f>
@@ -12708,15 +12750,32 @@
         <v>www.pornhub.com</v>
       </c>
     </row>
-    <row r="145" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A145" s="17"/>
-      <c r="B145" s="17"/>
-      <c r="C145" s="17"/>
-      <c r="D145" s="17"/>
-      <c r="E145" s="17"/>
-      <c r="F145" s="17"/>
-      <c r="G145" s="17"/>
-      <c r="H145" s="17"/>
+    <row r="145" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A145" s="17" t="str">
+        <f>IF(ISBLANK(R145)=TRUE,"Pending","Done")</f>
+        <v>Pending</v>
+      </c>
+      <c r="B145" s="17" t="s">
+        <v>827</v>
+      </c>
+      <c r="C145" s="17">
+        <v>51</v>
+      </c>
+      <c r="D145" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="E145" s="17" t="s">
+        <v>816</v>
+      </c>
+      <c r="F145" s="17" t="s">
+        <v>828</v>
+      </c>
+      <c r="G145" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H145" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="I145" s="17"/>
       <c r="J145" s="17"/>
       <c r="K145" s="17"/>
@@ -12729,17 +12788,37 @@
       <c r="R145" s="17"/>
       <c r="S145" s="17"/>
       <c r="T145" s="17"/>
-      <c r="U145" s="17"/>
-    </row>
-    <row r="146" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A146" s="17"/>
-      <c r="B146" s="17"/>
-      <c r="C146" s="17"/>
-      <c r="D146" s="17"/>
-      <c r="E146" s="17"/>
-      <c r="F146" s="17"/>
-      <c r="G146" s="17"/>
-      <c r="H146" s="17"/>
+      <c r="U145" s="17" t="str" cm="1">
+        <f t="array" ref="U145">_xlfn.REGEXEXTRACT(B145,"(?&lt;=//)[^/]+")</f>
+        <v>tube.perverzija.com</v>
+      </c>
+    </row>
+    <row r="146" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="A146" s="17" t="str">
+        <f>IF(ISBLANK(R146)=TRUE,"Pending","Done")</f>
+        <v>Pending</v>
+      </c>
+      <c r="B146" s="17" t="s">
+        <v>829</v>
+      </c>
+      <c r="C146" s="17">
+        <v>50</v>
+      </c>
+      <c r="D146" s="17" t="s">
+        <v>692</v>
+      </c>
+      <c r="E146" s="17" t="s">
+        <v>810</v>
+      </c>
+      <c r="F146" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="G146" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H146" s="17" t="s">
+        <v>192</v>
+      </c>
       <c r="I146" s="17"/>
       <c r="J146" s="17"/>
       <c r="K146" s="17"/>
@@ -12752,17 +12831,36 @@
       <c r="R146" s="17"/>
       <c r="S146" s="17"/>
       <c r="T146" s="17"/>
-      <c r="U146" s="17"/>
-    </row>
-    <row r="147" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A147" s="17"/>
-      <c r="B147" s="17"/>
-      <c r="C147" s="17"/>
-      <c r="D147" s="17"/>
-      <c r="E147" s="17"/>
-      <c r="F147" s="17"/>
-      <c r="G147" s="17"/>
-      <c r="H147" s="17"/>
+      <c r="U146" s="17" t="str" cm="1">
+        <f t="array" ref="U146">_xlfn.REGEXEXTRACT(B146,"(?&lt;=//)[^/]+")</f>
+        <v>tube.perverzija.com</v>
+      </c>
+    </row>
+    <row r="147" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A147" s="17" t="s">
+        <v>831</v>
+      </c>
+      <c r="B147" s="17" t="s">
+        <v>833</v>
+      </c>
+      <c r="C147" s="17">
+        <v>10</v>
+      </c>
+      <c r="D147" s="17" t="s">
+        <v>729</v>
+      </c>
+      <c r="E147" s="17" t="s">
+        <v>729</v>
+      </c>
+      <c r="F147" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G147" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H147" s="17" t="s">
+        <v>116</v>
+      </c>
       <c r="I147" s="17"/>
       <c r="J147" s="17"/>
       <c r="K147" s="17"/>
@@ -12775,25 +12873,406 @@
       <c r="R147" s="17"/>
       <c r="S147" s="17"/>
       <c r="T147" s="17"/>
-      <c r="U147" s="17"/>
+      <c r="U147" s="17" t="str" cm="1">
+        <f t="array" ref="U147">_xlfn.REGEXEXTRACT(B147,"(?&lt;=//)[^/]+")</f>
+        <v>abbdsm.com</v>
+      </c>
+    </row>
+    <row r="148" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="A148" s="17" t="s">
+        <v>831</v>
+      </c>
+      <c r="B148" s="17" t="s">
+        <v>834</v>
+      </c>
+      <c r="C148" s="17">
+        <v>11</v>
+      </c>
+      <c r="D148" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="E148" s="17" t="s">
+        <v>729</v>
+      </c>
+      <c r="F148" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G148" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H148" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="I148" s="17" t="s">
+        <v>533</v>
+      </c>
+      <c r="J148" s="17"/>
+      <c r="K148" s="17"/>
+      <c r="L148" s="17"/>
+      <c r="M148" s="17"/>
+      <c r="N148" s="17"/>
+      <c r="O148" s="17"/>
+      <c r="P148" s="17"/>
+      <c r="Q148" s="17"/>
+      <c r="R148" s="17"/>
+      <c r="S148" s="17"/>
+      <c r="T148" s="17"/>
+      <c r="U148" s="17" t="str" cm="1">
+        <f t="array" ref="U148">_xlfn.REGEXEXTRACT(B148,"(?&lt;=//)[^/]+")</f>
+        <v>xhamster44.desi</v>
+      </c>
+    </row>
+    <row r="149" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="A149" s="17" t="s">
+        <v>831</v>
+      </c>
+      <c r="B149" s="17" t="s">
+        <v>835</v>
+      </c>
+      <c r="C149" s="17">
+        <v>0</v>
+      </c>
+      <c r="D149" s="17" t="s">
+        <v>796</v>
+      </c>
+      <c r="E149" s="17" t="s">
+        <v>729</v>
+      </c>
+      <c r="F149" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G149" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H149" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="I149" s="17"/>
+      <c r="J149" s="17"/>
+      <c r="K149" s="17"/>
+      <c r="L149" s="17"/>
+      <c r="M149" s="17"/>
+      <c r="N149" s="17"/>
+      <c r="O149" s="17"/>
+      <c r="P149" s="17"/>
+      <c r="Q149" s="17"/>
+      <c r="R149" s="17"/>
+      <c r="S149" s="17"/>
+      <c r="T149" s="17"/>
+      <c r="U149" s="17" t="str" cm="1">
+        <f t="array" ref="U149">_xlfn.REGEXEXTRACT(B149,"(?&lt;=//)[^/]+")</f>
+        <v>www.tubebdsm.com</v>
+      </c>
+    </row>
+    <row r="150" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="A150" s="17" t="s">
+        <v>831</v>
+      </c>
+      <c r="B150" s="17" t="s">
+        <v>836</v>
+      </c>
+      <c r="C150" s="17">
+        <v>0</v>
+      </c>
+      <c r="D150" s="17" t="s">
+        <v>796</v>
+      </c>
+      <c r="E150" s="17" t="s">
+        <v>729</v>
+      </c>
+      <c r="F150" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G150" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H150" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="I150" s="17"/>
+      <c r="J150" s="17"/>
+      <c r="K150" s="17"/>
+      <c r="L150" s="17"/>
+      <c r="M150" s="17"/>
+      <c r="N150" s="17"/>
+      <c r="O150" s="17"/>
+      <c r="P150" s="17"/>
+      <c r="Q150" s="17"/>
+      <c r="R150" s="17"/>
+      <c r="S150" s="17"/>
+      <c r="T150" s="17"/>
+      <c r="U150" s="17" t="str" cm="1">
+        <f t="array" ref="U150">_xlfn.REGEXEXTRACT(B150,"(?&lt;=//)[^/]+")</f>
+        <v>www.tubebdsm.com</v>
+      </c>
+    </row>
+    <row r="151" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="A151" s="17" t="s">
+        <v>831</v>
+      </c>
+      <c r="B151" s="17" t="s">
+        <v>832</v>
+      </c>
+      <c r="C151" s="17">
+        <v>0</v>
+      </c>
+      <c r="D151" s="17" t="s">
+        <v>796</v>
+      </c>
+      <c r="E151" s="17" t="s">
+        <v>729</v>
+      </c>
+      <c r="F151" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G151" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H151" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="I151" s="17"/>
+      <c r="J151" s="17"/>
+      <c r="K151" s="17"/>
+      <c r="L151" s="17"/>
+      <c r="M151" s="17"/>
+      <c r="N151" s="17"/>
+      <c r="O151" s="17"/>
+      <c r="P151" s="17"/>
+      <c r="Q151" s="17"/>
+      <c r="R151" s="17"/>
+      <c r="S151" s="17"/>
+      <c r="T151" s="17"/>
+      <c r="U151" s="17" t="str" cm="1">
+        <f t="array" ref="U151">_xlfn.REGEXEXTRACT(B151,"(?&lt;=//)[^/]+")</f>
+        <v>www.tubebdsm.com</v>
+      </c>
+    </row>
+    <row r="152" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="A152" s="17" t="str">
+        <f>IF(ISBLANK(R152)=TRUE,"Pending","Done")</f>
+        <v>Pending</v>
+      </c>
+      <c r="B152" s="17" t="s">
+        <v>830</v>
+      </c>
+      <c r="C152" s="17">
+        <v>99</v>
+      </c>
+      <c r="D152" s="17" t="s">
+        <v>729</v>
+      </c>
+      <c r="E152" s="17" t="s">
+        <v>729</v>
+      </c>
+      <c r="F152" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G152" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H152" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="I152" s="17"/>
+      <c r="J152" s="17"/>
+      <c r="K152" s="17"/>
+      <c r="L152" s="17"/>
+      <c r="M152" s="17"/>
+      <c r="N152" s="17"/>
+      <c r="O152" s="17"/>
+      <c r="P152" s="17"/>
+      <c r="Q152" s="17"/>
+      <c r="R152" s="17"/>
+      <c r="S152" s="17"/>
+      <c r="T152" s="17"/>
+      <c r="U152" s="17" t="str" cm="1">
+        <f t="array" ref="U152">_xlfn.REGEXEXTRACT(B152,"(?&lt;=//)[^/]+")</f>
+        <v>xhamster44.desi</v>
+      </c>
+    </row>
+    <row r="153" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="A153" s="17" t="str">
+        <f>IF(ISBLANK(R153)=TRUE,"Pending","Done")</f>
+        <v>Pending</v>
+      </c>
+      <c r="B153" s="17" t="s">
+        <v>837</v>
+      </c>
+      <c r="C153" s="17">
+        <v>0</v>
+      </c>
+      <c r="D153" s="17" t="s">
+        <v>796</v>
+      </c>
+      <c r="E153" s="17" t="s">
+        <v>729</v>
+      </c>
+      <c r="F153" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G153" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H153" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="I153" s="17"/>
+      <c r="J153" s="17"/>
+      <c r="K153" s="17"/>
+      <c r="L153" s="17"/>
+      <c r="M153" s="17"/>
+      <c r="N153" s="17"/>
+      <c r="O153" s="17"/>
+      <c r="P153" s="17"/>
+      <c r="Q153" s="17"/>
+      <c r="R153" s="17"/>
+      <c r="S153" s="17"/>
+      <c r="T153" s="17"/>
+      <c r="U153" s="17" t="str" cm="1">
+        <f t="array" ref="U153">_xlfn.REGEXEXTRACT(B153,"(?&lt;=//)[^/]+")</f>
+        <v>www.tubebdsm.com</v>
+      </c>
+    </row>
+    <row r="154" spans="1:21" ht="60" x14ac:dyDescent="0.25">
+      <c r="A154" s="17" t="str">
+        <f>IF(ISBLANK(R154)=TRUE,"Pending","Done")</f>
+        <v>Pending</v>
+      </c>
+      <c r="B154" s="17" t="s">
+        <v>841</v>
+      </c>
+      <c r="C154" s="17">
+        <v>44</v>
+      </c>
+      <c r="D154" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="E154" s="17" t="s">
+        <v>729</v>
+      </c>
+      <c r="F154" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G154" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H154" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="I154" s="17"/>
+      <c r="J154" s="17"/>
+      <c r="K154" s="17"/>
+      <c r="L154" s="17"/>
+      <c r="M154" s="17"/>
+      <c r="N154" s="17"/>
+      <c r="O154" s="17"/>
+      <c r="P154" s="17"/>
+      <c r="Q154" s="17"/>
+      <c r="R154" s="17"/>
+      <c r="S154" s="17"/>
+      <c r="T154" s="17"/>
+      <c r="U154" s="17"/>
+    </row>
+    <row r="155" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A155" s="17" t="str">
+        <f>IF(ISBLANK(R155)=TRUE,"Pending","Done")</f>
+        <v>Pending</v>
+      </c>
+      <c r="B155" s="17" t="s">
+        <v>839</v>
+      </c>
+      <c r="C155" s="17">
+        <v>21</v>
+      </c>
+      <c r="D155" s="17" t="s">
+        <v>840</v>
+      </c>
+      <c r="E155" s="17" t="s">
+        <v>840</v>
+      </c>
+      <c r="F155" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G155" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H155" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="I155" s="17"/>
+      <c r="J155" s="17"/>
+      <c r="K155" s="17"/>
+      <c r="L155" s="17"/>
+      <c r="M155" s="17"/>
+      <c r="N155" s="17"/>
+      <c r="O155" s="17"/>
+      <c r="P155" s="17"/>
+      <c r="Q155" s="17"/>
+      <c r="R155" s="17"/>
+      <c r="S155" s="17"/>
+      <c r="T155" s="17"/>
+      <c r="U155" s="17" t="str" cm="1">
+        <f t="array" ref="U155">_xlfn.REGEXEXTRACT(B155,"(?&lt;=//)[^/]+")</f>
+        <v>xhamster44.desi</v>
+      </c>
+    </row>
+    <row r="156" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="A156" s="17" t="str">
+        <f>IF(ISBLANK(R156)=TRUE,"Pending","Done")</f>
+        <v>Pending</v>
+      </c>
+      <c r="B156" s="17" t="s">
+        <v>838</v>
+      </c>
+      <c r="C156" s="17">
+        <v>0</v>
+      </c>
+      <c r="D156" s="17" t="s">
+        <v>796</v>
+      </c>
+      <c r="E156" s="17" t="s">
+        <v>729</v>
+      </c>
+      <c r="F156" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G156" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H156" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="I156" s="17"/>
+      <c r="J156" s="17"/>
+      <c r="K156" s="17"/>
+      <c r="L156" s="17"/>
+      <c r="M156" s="17"/>
+      <c r="N156" s="17"/>
+      <c r="O156" s="17"/>
+      <c r="P156" s="17"/>
+      <c r="Q156" s="17"/>
+      <c r="R156" s="17"/>
+      <c r="S156" s="17"/>
+      <c r="T156" s="17"/>
+      <c r="U156" s="17" t="str" cm="1">
+        <f t="array" ref="U156">_xlfn.REGEXEXTRACT(B156,"(?&lt;=//)[^/]+")</f>
+        <v>www.tubebdsm.com</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U148" xr:uid="{84BC93B7-B882-48B2-AAF6-D1E0B3702CB8}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U148">
-      <sortCondition descending="1" ref="S1:S148"/>
-    </sortState>
-  </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:U149">
-    <sortCondition ref="C1:C149"/>
+  <autoFilter ref="A1:U156" xr:uid="{84BC93B7-B882-48B2-AAF6-D1E0B3702CB8}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U156">
+    <sortCondition descending="1" ref="S1:S156"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:U125 A149:XFD1048576 V148:XFD148 A126:XFD147">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+  <conditionalFormatting sqref="A1:U125 A126:XFD1048576">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S149:S1048576 S1:S147">
-    <cfRule type="colorScale" priority="12">
+  <conditionalFormatting sqref="S1:S1048576">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
